--- a/Unity/Assets/Config/Excel/SkillSocketConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillSocketConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>101000131,101000132</t>
+  </si>
+  <si>
+    <t>101001121,101001122</t>
+  </si>
+  <si>
+    <t>101001131,101001132</t>
   </si>
 </sst>
 </file>
@@ -11275,7 +11281,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{1ABDD4B0-47A0-45B6-BFBE-5A216D020D2D}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{3965249A-5260-4B32-80E5-3C4B15C413BA}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11680,6 +11686,20 @@
         <v>18</v>
       </c>
     </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="2">
+        <v>1010011</v>
+      </c>
+      <c r="D5" s="2">
+        <v>101001111</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="8" spans="1:8">
       <c r="F8" s="7"/>
     </row>
